--- a/frontend/public/example_kunjungan_posyandu.xlsx
+++ b/frontend/public/example_kunjungan_posyandu.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSI\Documents\khoir\freelance\test\pops_apps\frontend\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSI\Documents\khoir\freelance\latest\pops_apps\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61F0A69-0DA1-4F3D-A39D-3768D9B48605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F247F017-E339-4517-80B8-7A7EB5F82BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="example_kunjungan_posyandu(4)" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="150">
   <si>
     <t>No</t>
   </si>
@@ -190,10 +191,286 @@
     <t>-</t>
   </si>
   <si>
-    <t>Pemberian Vit A</t>
-  </si>
-  <si>
     <t>`1871000000000033</t>
+  </si>
+  <si>
+    <t>Cara Ukur</t>
+  </si>
+  <si>
+    <t>Kelas Ibu Balita</t>
+  </si>
+  <si>
+    <t>MBG</t>
+  </si>
+  <si>
+    <t>Berdiri</t>
+  </si>
+  <si>
+    <t>ANDI PRATAMA</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>SUTRISNO</t>
+  </si>
+  <si>
+    <t>4 Tahun - 3 Bulan</t>
+  </si>
+  <si>
+    <t>13,2</t>
+  </si>
+  <si>
+    <t>-1,2</t>
+  </si>
+  <si>
+    <t>Pendek</t>
+  </si>
+  <si>
+    <t>-2,4</t>
+  </si>
+  <si>
+    <t>Gizi Kurang</t>
+  </si>
+  <si>
+    <t>-2,1</t>
+  </si>
+  <si>
+    <t>Sesuai</t>
+  </si>
+  <si>
+    <t>Ada</t>
+  </si>
+  <si>
+    <t>Aktif</t>
+  </si>
+  <si>
+    <t>Ya</t>
+  </si>
+  <si>
+    <t>Tinggi kurang</t>
+  </si>
+  <si>
+    <t>SITI AMINAH</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>25/08/2020</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>RAHMAWATI</t>
+  </si>
+  <si>
+    <t>ANGGREK</t>
+  </si>
+  <si>
+    <t>4 Tahun - 10 Bulan</t>
+  </si>
+  <si>
+    <t>12,1</t>
+  </si>
+  <si>
+    <t>-2,5</t>
+  </si>
+  <si>
+    <t>Sangat Pendek</t>
+  </si>
+  <si>
+    <t>-3,2</t>
+  </si>
+  <si>
+    <t>Kurus</t>
+  </si>
+  <si>
+    <t>-2,8</t>
+  </si>
+  <si>
+    <t>Tidak</t>
+  </si>
+  <si>
+    <t>Perlu intervensi</t>
+  </si>
+  <si>
+    <t>BUDI SETIAWAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>WARNO</t>
+  </si>
+  <si>
+    <t>MAWAR</t>
+  </si>
+  <si>
+    <t>3 Tahun - 5 Bulan</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>-0,5</t>
+  </si>
+  <si>
+    <t>-0,8</t>
+  </si>
+  <si>
+    <t>-0,6</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Sehat</t>
+  </si>
+  <si>
+    <t>DEWI LESTARI</t>
+  </si>
+  <si>
+    <t>18/11/2021</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>SURYANI</t>
+  </si>
+  <si>
+    <t>KENANGA</t>
+  </si>
+  <si>
+    <t>3 Tahun - 7 Bulan</t>
+  </si>
+  <si>
+    <t>11,8</t>
+  </si>
+  <si>
+    <t>-2,3</t>
+  </si>
+  <si>
+    <t>BB kurang</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>NUR AISYAH</t>
+  </si>
+  <si>
+    <t>14/02/2021</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>AHMAD</t>
+  </si>
+  <si>
+    <t>TULIP</t>
+  </si>
+  <si>
+    <t>4 Tahun - 4 Bulan</t>
+  </si>
+  <si>
+    <t>12,5</t>
+  </si>
+  <si>
+    <t>-3,0</t>
+  </si>
+  <si>
+    <t>-2,2</t>
+  </si>
+  <si>
+    <t>Tinggi sangat rendah</t>
+  </si>
+  <si>
+    <t>`1871000000000030</t>
+  </si>
+  <si>
+    <t>`1871000000000031</t>
+  </si>
+  <si>
+    <t>`1871000000000032</t>
+  </si>
+  <si>
+    <t>`1871000000000035</t>
+  </si>
+  <si>
+    <t>FARHAN MAULANA</t>
+  </si>
+  <si>
+    <t>ROHMAN</t>
+  </si>
+  <si>
+    <t>2 Tahun - 1 Bulan</t>
+  </si>
+  <si>
+    <t>12,0</t>
+  </si>
+  <si>
+    <t>-0,9</t>
+  </si>
+  <si>
+    <t>-0,7</t>
+  </si>
+  <si>
+    <t>Perkembangan baik</t>
+  </si>
+  <si>
+    <t>NADIA PUTRI</t>
+  </si>
+  <si>
+    <t>22/04/2022</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>SITI</t>
+  </si>
+  <si>
+    <t>3 Tahun - 2 Bulan</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>TB kurang dari standar</t>
+  </si>
+  <si>
+    <t>`1871000000000040</t>
+  </si>
+  <si>
+    <t>`1871000000000042</t>
+  </si>
+  <si>
+    <t>`3223000000000030</t>
+  </si>
+  <si>
+    <t>`3223000000000031</t>
+  </si>
+  <si>
+    <t>`3223000000000033</t>
+  </si>
+  <si>
+    <t>`3223000000000034</t>
+  </si>
+  <si>
+    <t>`3223000000000035</t>
+  </si>
+  <si>
+    <t>`3223000000000036</t>
+  </si>
+  <si>
+    <t>`3223000000000037</t>
+  </si>
+  <si>
+    <t>MendapaMakan Bergizi Gratis</t>
   </si>
 </sst>
 </file>
@@ -234,14 +511,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,14 +797,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -590,61 +868,70 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:40">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -653,7 +940,7 @@
         <v>38</v>
       </c>
       <c r="E2" s="1">
-        <v>44111</v>
+        <v>45572</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -694,7 +981,7 @@
       <c r="R2" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>47</v>
       </c>
       <c r="T2" t="s">
@@ -703,41 +990,1011 @@
       <c r="U2">
         <v>105</v>
       </c>
-      <c r="V2">
+      <c r="V2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W2">
         <v>15</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>52</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>53</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>54</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>55</v>
       </c>
       <c r="AF2" t="s">
         <v>55</v>
       </c>
-      <c r="AK2" t="s">
-        <v>56</v>
+      <c r="AG2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FE07D6-2BA7-4FAD-AA18-71177F097000}">
+  <dimension ref="A1:AM8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="3">
+        <v>44533</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2">
+        <v>95</v>
+      </c>
+      <c r="V2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W2">
+        <v>14</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE2">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3">
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" t="s">
+        <v>81</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" t="s">
+        <v>82</v>
+      </c>
+      <c r="S3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3">
+        <v>90</v>
+      </c>
+      <c r="V3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W3">
+        <v>13</v>
+      </c>
+      <c r="X3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="3">
+        <v>44682</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" t="s">
+        <v>96</v>
+      </c>
+      <c r="U4">
+        <v>98</v>
+      </c>
+      <c r="V4" t="s">
+        <v>60</v>
+      </c>
+      <c r="W4">
+        <v>15</v>
+      </c>
+      <c r="X4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE4">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>107</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" t="s">
+        <v>108</v>
+      </c>
+      <c r="U5">
+        <v>92</v>
+      </c>
+      <c r="V5" t="s">
+        <v>60</v>
+      </c>
+      <c r="W5">
+        <v>13</v>
+      </c>
+      <c r="X5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6">
+        <v>48</v>
+      </c>
+      <c r="H6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" t="s">
+        <v>116</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" t="s">
+        <v>117</v>
+      </c>
+      <c r="S6" t="s">
+        <v>47</v>
+      </c>
+      <c r="T6" t="s">
+        <v>118</v>
+      </c>
+      <c r="U6">
+        <v>91</v>
+      </c>
+      <c r="V6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W6">
+        <v>13</v>
+      </c>
+      <c r="X6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="3">
+        <v>45204</v>
+      </c>
+      <c r="F7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7" t="s">
+        <v>128</v>
+      </c>
+      <c r="S7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T7" t="s">
+        <v>129</v>
+      </c>
+      <c r="U7">
+        <v>86</v>
+      </c>
+      <c r="V7" t="s">
+        <v>60</v>
+      </c>
+      <c r="W7">
+        <v>14</v>
+      </c>
+      <c r="X7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8" t="s">
+        <v>137</v>
+      </c>
+      <c r="S8" t="s">
+        <v>47</v>
+      </c>
+      <c r="T8" t="s">
+        <v>138</v>
+      </c>
+      <c r="U8">
+        <v>88</v>
+      </c>
+      <c r="V8" t="s">
+        <v>60</v>
+      </c>
+      <c r="W8">
+        <v>13</v>
+      </c>
+      <c r="X8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/frontend/public/example_kunjungan_posyandu.xlsx
+++ b/frontend/public/example_kunjungan_posyandu.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSI\Documents\khoir\freelance\latest\pops_apps\frontend\public\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8E8D06-FE3D-43EE-BD14-4B6487D71822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="example_kunjungan_posyandu(4)" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="124">
   <si>
     <t>No</t>
   </si>
@@ -85,6 +79,9 @@
     <t>Tinggi</t>
   </si>
   <si>
+    <t>Cara Ukur</t>
+  </si>
+  <si>
     <t>LiLA</t>
   </si>
   <si>
@@ -118,21 +115,30 @@
     <t>KIA</t>
   </si>
   <si>
+    <t>Kelas Ibu Balita</t>
+  </si>
+  <si>
+    <t>MBG</t>
+  </si>
+  <si>
     <t>Detail</t>
   </si>
   <si>
-    <t>Mendapatkan Bantuan</t>
-  </si>
-  <si>
-    <t>no_kk</t>
-  </si>
-  <si>
-    <t>catatan</t>
+    <t>`1871000000000030</t>
+  </si>
+  <si>
+    <t>ANDI PRATAMA</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>SUTRISNO</t>
+  </si>
+  <si>
     <t>JAWA TENGAH</t>
   </si>
   <si>
@@ -148,231 +154,204 @@
     <t>MELATI</t>
   </si>
   <si>
+    <t>4 Tahun - 3 Bulan</t>
+  </si>
+  <si>
     <t>16/06/2025</t>
   </si>
   <si>
+    <t>13,2</t>
+  </si>
+  <si>
+    <t>Berdiri</t>
+  </si>
+  <si>
     <t>Normal</t>
   </si>
   <si>
+    <t>-1,2</t>
+  </si>
+  <si>
+    <t>Pendek</t>
+  </si>
+  <si>
+    <t>-2,4</t>
+  </si>
+  <si>
+    <t>Gizi Buruk</t>
+  </si>
+  <si>
+    <t>-2,1</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Sesuai</t>
+  </si>
+  <si>
+    <t>Ada</t>
+  </si>
+  <si>
+    <t>Aktif</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>`1871000000000031</t>
+  </si>
+  <si>
+    <t>SITI AMINAH</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>25/08/2020</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>RAHMAWATI</t>
+  </si>
+  <si>
+    <t>ANGGREK</t>
+  </si>
+  <si>
+    <t>4 Tahun - 10 Bulan</t>
+  </si>
+  <si>
+    <t>12,1</t>
+  </si>
+  <si>
+    <t>Kurang</t>
+  </si>
+  <si>
+    <t>-2,5</t>
+  </si>
+  <si>
+    <t>Sangat Pendek</t>
+  </si>
+  <si>
+    <t>-3,2</t>
+  </si>
+  <si>
+    <t>Gizi Kurang</t>
+  </si>
+  <si>
+    <t>-2,8</t>
+  </si>
+  <si>
+    <t>Tidak</t>
+  </si>
+  <si>
+    <t>`1871000000000032</t>
+  </si>
+  <si>
+    <t>BUDI SETIAWAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>WARNO</t>
+  </si>
+  <si>
+    <t>MAWAR</t>
+  </si>
+  <si>
+    <t>3 Tahun - 5 Bulan</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>-0,5</t>
+  </si>
+  <si>
+    <t>-0,8</t>
+  </si>
+  <si>
     <t>Gizi Baik</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>-0,6</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>`1871000000000033</t>
   </si>
   <si>
-    <t>Cara Ukur</t>
-  </si>
-  <si>
-    <t>Kelas Ibu Balita</t>
-  </si>
-  <si>
-    <t>MBG</t>
-  </si>
-  <si>
-    <t>Berdiri</t>
-  </si>
-  <si>
-    <t>ANDI PRATAMA</t>
-  </si>
-  <si>
-    <t>3,1</t>
-  </si>
-  <si>
-    <t>SUTRISNO</t>
-  </si>
-  <si>
-    <t>4 Tahun - 3 Bulan</t>
-  </si>
-  <si>
-    <t>13,2</t>
-  </si>
-  <si>
-    <t>-1,2</t>
-  </si>
-  <si>
-    <t>Pendek</t>
-  </si>
-  <si>
-    <t>-2,4</t>
-  </si>
-  <si>
-    <t>Gizi Kurang</t>
-  </si>
-  <si>
-    <t>-2,1</t>
-  </si>
-  <si>
-    <t>Sesuai</t>
-  </si>
-  <si>
-    <t>Ada</t>
-  </si>
-  <si>
-    <t>Aktif</t>
+    <t>DEWI LESTARI</t>
+  </si>
+  <si>
+    <t>18/11/2021</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>SURYANI</t>
+  </si>
+  <si>
+    <t>KENANGA</t>
+  </si>
+  <si>
+    <t>3 Tahun - 7 Bulan</t>
+  </si>
+  <si>
+    <t>11,8</t>
+  </si>
+  <si>
+    <t>-2,3</t>
   </si>
   <si>
     <t>Ya</t>
   </si>
   <si>
-    <t>Tinggi kurang</t>
-  </si>
-  <si>
-    <t>SITI AMINAH</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>25/08/2020</t>
-  </si>
-  <si>
-    <t>2,7</t>
-  </si>
-  <si>
-    <t>RAHMAWATI</t>
-  </si>
-  <si>
-    <t>ANGGREK</t>
-  </si>
-  <si>
-    <t>4 Tahun - 10 Bulan</t>
-  </si>
-  <si>
-    <t>12,1</t>
-  </si>
-  <si>
-    <t>-2,5</t>
-  </si>
-  <si>
-    <t>Sangat Pendek</t>
-  </si>
-  <si>
-    <t>-3,2</t>
-  </si>
-  <si>
-    <t>-2,8</t>
-  </si>
-  <si>
-    <t>Tidak</t>
-  </si>
-  <si>
-    <t>Perlu intervensi</t>
-  </si>
-  <si>
-    <t>BUDI SETIAWAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>WARNO</t>
-  </si>
-  <si>
-    <t>MAWAR</t>
-  </si>
-  <si>
-    <t>3 Tahun - 5 Bulan</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>-0,5</t>
-  </si>
-  <si>
-    <t>-0,8</t>
-  </si>
-  <si>
-    <t>-0,6</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Sehat</t>
-  </si>
-  <si>
-    <t>DEWI LESTARI</t>
-  </si>
-  <si>
-    <t>18/11/2021</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>SURYANI</t>
-  </si>
-  <si>
-    <t>KENANGA</t>
-  </si>
-  <si>
-    <t>3 Tahun - 7 Bulan</t>
-  </si>
-  <si>
-    <t>11,8</t>
-  </si>
-  <si>
-    <t>-2,3</t>
-  </si>
-  <si>
-    <t>BB kurang</t>
+    <t>`1871000000000035</t>
+  </si>
+  <si>
+    <t>NUR AISYAH</t>
+  </si>
+  <si>
+    <t>14/02/2021</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>AHMAD</t>
+  </si>
+  <si>
+    <t>TULIP</t>
+  </si>
+  <si>
+    <t>4 Tahun - 4 Bulan</t>
+  </si>
+  <si>
+    <t>12,5</t>
+  </si>
+  <si>
+    <t>-3,0</t>
+  </si>
+  <si>
+    <t>-2,2</t>
+  </si>
+  <si>
+    <t>`1871000000000040</t>
+  </si>
+  <si>
+    <t>FARHAN MAULANA</t>
   </si>
   <si>
     <t>3,0</t>
   </si>
   <si>
-    <t>NUR AISYAH</t>
-  </si>
-  <si>
-    <t>14/02/2021</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>AHMAD</t>
-  </si>
-  <si>
-    <t>TULIP</t>
-  </si>
-  <si>
-    <t>4 Tahun - 4 Bulan</t>
-  </si>
-  <si>
-    <t>12,5</t>
-  </si>
-  <si>
-    <t>-3,0</t>
-  </si>
-  <si>
-    <t>-2,2</t>
-  </si>
-  <si>
-    <t>Tinggi sangat rendah</t>
-  </si>
-  <si>
-    <t>`1871000000000030</t>
-  </si>
-  <si>
-    <t>`1871000000000031</t>
-  </si>
-  <si>
-    <t>`1871000000000032</t>
-  </si>
-  <si>
-    <t>`1871000000000035</t>
-  </si>
-  <si>
-    <t>FARHAN MAULANA</t>
-  </si>
-  <si>
     <t>ROHMAN</t>
   </si>
   <si>
@@ -388,7 +367,7 @@
     <t>-0,7</t>
   </si>
   <si>
-    <t>Perkembangan baik</t>
+    <t>`1871000000000042</t>
   </si>
   <si>
     <t>NADIA PUTRI</t>
@@ -407,52 +386,19 @@
   </si>
   <si>
     <t>11,5</t>
-  </si>
-  <si>
-    <t>TB kurang dari standar</t>
-  </si>
-  <si>
-    <t>`1871000000000040</t>
-  </si>
-  <si>
-    <t>`1871000000000042</t>
-  </si>
-  <si>
-    <t>`3223000000000030</t>
-  </si>
-  <si>
-    <t>`3223000000000031</t>
-  </si>
-  <si>
-    <t>`3223000000000033</t>
-  </si>
-  <si>
-    <t>`3223000000000034</t>
-  </si>
-  <si>
-    <t>`3223000000000035</t>
-  </si>
-  <si>
-    <t>`3223000000000036</t>
-  </si>
-  <si>
-    <t>`3223000000000037</t>
-  </si>
-  <si>
-    <t>Mendapatkan Makan Bergizi Gratis</t>
-  </si>
-  <si>
-    <t>Kurang</t>
-  </si>
-  <si>
-    <t>Gizi Buruk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,19 +410,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -484,34 +760,321 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -769,20 +1332,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AJ10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="9.55833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,105 +1410,93 @@
         <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AI1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AJ1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="1">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2">
         <v>44533</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O2">
         <v>3</v>
@@ -954,111 +1505,105 @@
         <v>2</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="U2">
         <v>95</v>
       </c>
       <c r="V2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W2">
         <v>14</v>
       </c>
       <c r="X2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AB2" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="AC2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AD2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AE2">
         <v>2</v>
       </c>
       <c r="AF2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AG2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AI2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -1067,111 +1612,105 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="U3">
         <v>90</v>
       </c>
       <c r="V3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W3">
         <v>13</v>
       </c>
-      <c r="X3" s="2" t="s">
-        <v>140</v>
+      <c r="X3" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s">
         <v>75</v>
       </c>
-      <c r="Z3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>78</v>
-      </c>
       <c r="AD3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AE3">
         <v>2</v>
       </c>
       <c r="AF3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AI3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="1">
+        <v>38</v>
+      </c>
+      <c r="E4" s="2">
         <v>44682</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G4">
         <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O4">
         <v>2</v>
@@ -1180,111 +1719,105 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="U4">
         <v>98</v>
       </c>
       <c r="V4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W4">
         <v>15</v>
       </c>
       <c r="X4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC4" t="s">
         <v>87</v>
       </c>
-      <c r="Z4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA4" t="s">
+      <c r="AD4" t="s">
         <v>88</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>90</v>
       </c>
       <c r="AE4">
         <v>2</v>
       </c>
       <c r="AF4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AG4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AI4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
         <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" t="s">
-        <v>94</v>
       </c>
       <c r="G5">
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O5">
         <v>4</v>
@@ -1293,114 +1826,105 @@
         <v>2</v>
       </c>
       <c r="Q5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U5">
         <v>92</v>
       </c>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W5">
         <v>13</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>140</v>
+      <c r="X5" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="Y5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Z5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AA5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AD5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AE5">
         <v>1</v>
       </c>
       <c r="AF5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AI5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" t="s">
-        <v>104</v>
       </c>
       <c r="G6">
         <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1409,114 +1933,105 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U6">
         <v>91</v>
       </c>
       <c r="V6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W6">
         <v>13</v>
       </c>
-      <c r="X6" s="2" t="s">
-        <v>140</v>
+      <c r="X6" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="Y6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Z6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AA6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AB6" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AE6">
         <v>2</v>
       </c>
       <c r="AF6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AI6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="1">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2">
         <v>45204</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -1525,111 +2040,105 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="S7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="U7">
         <v>86</v>
       </c>
       <c r="V7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W7">
         <v>14</v>
       </c>
       <c r="X7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Y7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD7" t="s">
         <v>88</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>90</v>
       </c>
       <c r="AE7">
         <v>1</v>
       </c>
       <c r="AF7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AG7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AI7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>137</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G8">
         <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -1638,73 +2147,103 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="S8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="U8">
         <v>88</v>
       </c>
       <c r="V8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="W8">
         <v>13</v>
       </c>
-      <c r="X8" s="2" t="s">
-        <v>140</v>
+      <c r="X8" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AA8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AB8" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="AC8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AD8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AE8">
         <v>1</v>
       </c>
       <c r="AF8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AH8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>138</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>129</v>
-      </c>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>